--- a/02_加值成品/八下/八下1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-2 質量守恆定律　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下1-2 質量守恆定律　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>化學反應前後總質量？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>所有化學反應</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>結合了氧</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>質量守恆定律由誰提出？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>拉瓦節</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>結合了氧</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>所有化學反應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>科學史</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>反應中原子種類數目？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>氣體逸散</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>結合了氧</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>涉及氣體反應要在什麼系統測？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>所有化學反應</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氣體逸散</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>密閉</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>結合了氧</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>防逸散</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>質量守恆是因原子？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>重新組合</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>所有化學反應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>憑空生滅</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>不生滅</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>反應物10g生成物應？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>16g</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>20g</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>拉瓦節推翻了什麼學說？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>燃素說</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>開啟定量化學</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>舊理論</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>質量守恆適用哪些反應？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>拉瓦節</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>所有化學反應</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>普遍</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>化學反應前後原子的種類與數目？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>拉瓦節</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>質量守恆是因為原子不會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>開啟定量化學</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>憑空生滅</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>拉瓦節</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-2 質量守恆定律　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下1-2 質量守恆定律　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>A2g+B3g→C?g</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>0.16g</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>20g</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>12g</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>4g甲烷+16g氧→?g產物</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>10g</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>12g</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>0.16g</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>鐵生鏽後變重因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>結合了氧</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>含氧</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>木材燃燒後灰燼變輕因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>氣體逸散</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>憑空生滅</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>密閉則守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>密閉瓶內反應總質量？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>氣體逸散</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>燃素說</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>反應物共28g,生成物一個12g,另一個？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>20g</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>16g</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>0.16g</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>88g</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>燃素說錯在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>未考慮氣體參與</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>放出CO₂逸散</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>用密閉容器反應前後秤重</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>氣體產物逸散未計入</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>舊觀</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>鎂燃燒生成氧化鎂,質量增加來自？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>空氣中的氧</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>開啟定量化學</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>憑空生滅</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>5g物質A與7g物質B完全反應生成物？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>20g</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>10g</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>88g</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>燃燒後密閉容器內總質量會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>空氣中的氧</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>所有化學反應</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>密閉守恆</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-2 質量守恆定律　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下1-2 質量守恆定律　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何開放燃燒木材看似不守恆？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>放出CO₂逸散</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>用密閉容器反應前後秤重</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>生成CO₂等氣體逸散,未計入</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>氣體產物逸散未計入</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>系統邊界</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>鎂帶0.24g在空氣燃燒得0.40g氧化鎂,結合氧？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>12g</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>16g</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>0.16g</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>守恆計算</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>如何設計實驗驗證含氣體反應守恆？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>原子既不生成也不消滅只重排</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>氣體產物逸散未計入</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>未考慮氣體參與</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>用密閉容器反應前後秤重</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>密閉</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>質量守恆的微觀解釋？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>原子既不生成也不消滅只重排</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>放出CO₂逸散</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>未考慮氣體參與</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>生成CO₂等氣體逸散,未計入</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>原子觀</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>封閉燒瓶內鐵絲燃燒,總質量變嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>憑空生滅</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>所有化學反應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>密閉</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>密閉守恆</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>拉瓦節的貢獻對化學意義？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>拉瓦節</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>開啟定量化學</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>重新組合</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>科學史</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>鹽酸與大理石在開放容器反應變輕因？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>放出CO₂逸散</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>氣體產物逸散未計入</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>原子既不生成也不消滅只重排</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>生成CO₂等氣體逸散,未計入</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>氣體</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>56g鐵完全反應需32g氧,生成氧化鐵?g</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>12g</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>0.4g</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>20g</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>88g</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>鎂0.6g燃燒得1.0g氧化鎂結合氧？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>16g</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>20g</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>0.4g</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何開放系統燃燒常看似質量減少？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>未考慮氣體參與</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>氣體產物逸散未計入</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>原子既不生成也不消滅只重排</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>放出CO₂逸散</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：原子在反應前後只是重新排列，沒有增加也沒有消失，所以總質量維持一樣</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>科學史</t>
+          <t>科學史：法國科學家拉瓦節用密閉容器做燃燒實驗，發現反應前後質量不變，因而提出這個定律</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：化學反應只是把原子重新組合成新物質，原子本身的種類和數目都不會改變</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>防逸散</t>
+          <t>防逸散：如果容器沒有密封，產生的氣體會跑到空氣中，秤起來質量就會看起來變少</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>不生滅</t>
+          <t>不生滅：原子在化學反應中不會憑空產生也不會憑空消失，只是換了組合方式</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：因為反應前後原子總數不變，所以生成物的總質量會等於反應物的總質量</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>舊理論</t>
+          <t>舊理論：燃素說認為燃燒是釋放出一種叫燃素的物質，拉瓦節用實驗證明燃燒其實是與氧結合</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>普遍</t>
+          <t>普遍：不管是燃燒、生鏽還是中和，只要是化學反應，質量守恆定律都成立</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：化學反應只是原子重新排列組合成新物質，原子的種類和數目在反應前後都不會改變</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：質量守恆定律成立的根本原因，是原子在化學反應中不會憑空產生也不會憑空消失，只是重新組合</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：反應物A和B的質量加起來是2+3=5克，生成物C的質量也會是5克</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：兩個反應物的質量相加是4+16=20克，生成物的總質量也會是20克</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>含氧</t>
+          <t>含氧：鐵生鏽時和空氣中的氧結合，多出來的氧原子加入鐵中，所以整體質量變重了</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>密閉則守恆</t>
+          <t>密閉則守恆：木材燃燒會產生二氧化碳等氣體飛散到空氣中，若把氣體也秤進去，總質量其實沒變</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：因為瓶子是密封的，所有反應產生的氣體都留在瓶內，秤重時質量不會改變</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：生成物總質量要等於反應物總質量28克，扣掉已知的12克，剩下就是16克</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>舊觀</t>
+          <t>舊觀：燃素說沒有想到燃燒其實是物質和空氣中的氧結合，才會誤以為燃燒後會變輕</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>結合：鎂在空氣中燃燒時會和氧氣結合成氧化鎂，多出來的重量就是結合進去的氧</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：根據質量守恆定律，反應前後總質量不變，5克加7克等於12克，全部反應物的質量都會出現在生成物中</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>密閉守恆</t>
+          <t>密閉守恆：只要是在密閉容器內反應，沒有氣體逸散出去，反應前後容器內的總質量會維持不變，符合質量守恆定律</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>系統邊界</t>
+          <t>系統邊界：燃燒產生的二氧化碳等氣體飛到空氣中沒被秤到，才會誤以為質量減少了</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>守恆計算</t>
+          <t>守恆計算：氧化鎂的質量減去原本鎂帶的質量，0.40減0.24等於0.16克，就是結合進去的氧</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>密閉</t>
+          <t>密閉：把反應物裝在密封容器中，反應前後分別秤重，若質量相同就證實了守恆</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>原子觀</t>
+          <t>原子觀：從原子的角度看，化學反應只是打斷舊鍵、形成新鍵，原子本身完全沒有增減</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>密閉守恆</t>
+          <t>密閉守恆：燒瓶密封後氧氣和產生的氣體都留在瓶內，所以整體質量在反應前後保持相同</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>科學史</t>
+          <t>科學史：拉瓦節用精確秤重的方法研究反應，讓化學從描述性學問變成能精準計算的科學</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>氣體</t>
+          <t>氣體：反應會產生二氧化碳氣體跑出容器，沒被秤進去，所以看起來質量減少了</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：反應物鐵和氧的質量相加是56加32等於88克，生成物氧化鐵的質量也會是88克</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：氧化鎂的質量等於鎂加上結合的氧，1.0克減去鎂原本的0.6克，代表結合了0.4克的氧</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>系統</t>
+          <t>系統：在開放空間燃燒時，產生的氣體(如二氧化碳、水蒸氣)會飄散到空氣中沒被秤到，看起來質量好像減少了，但其實只是沒有把逸散的氣體質量算進去，總質量其實仍然守恆</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下1-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-2_三種難度測驗卷.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>20g</t>
+          <t>10g</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>0.16g</t>
+          <t>5g</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>88g</t>
+          <t>12g</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>16g</t>
+          <t>88g</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>5g</t>
+          <t>20g</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
